--- a/pesaje/analytica/Report/Pesaje-Libre-Export-Base.xlsx
+++ b/pesaje/analytica/Report/Pesaje-Libre-Export-Base.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\projects\minersoft-projects\minersoft\acopio-project-configuration\pesaje\analytica\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF9EBD54-E699-4A35-AEA0-96454072B816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F15F58-0B28-4422-BDB6-299E8BE50AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,9 +78,6 @@
     <t>PESO NETO</t>
   </si>
   <si>
-    <t>ENVASE</t>
-  </si>
-  <si>
     <t>PESAJE LIBRE</t>
   </si>
   <si>
@@ -88,6 +85,9 @@
   </si>
   <si>
     <t>ESTADO PESAJE LIBRE</t>
+  </si>
+  <si>
+    <t>PLACA</t>
   </si>
 </sst>
 </file>
@@ -780,7 +780,7 @@
     </row>
     <row r="8" spans="1:40" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
@@ -792,7 +792,7 @@
         <v>6</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>9</v>
@@ -801,7 +801,7 @@
         <v>4</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>10</v>
@@ -828,7 +828,7 @@
         <v>16</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:40" s="4" customFormat="1" x14ac:dyDescent="0.3"/>
